--- a/SeleniumProject/TestData/CheckoutData.xlsx
+++ b/SeleniumProject/TestData/CheckoutData.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\PTTKPM\THI\Gbao\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\source\repos\SeleniumProject\SeleniumProject\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9BD9B36E-36BD-4B27-A3CA-D893B124B3A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F924B55-DD65-40D2-BC1F-8A5ADFF27726}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{9521ABCA-C582-4982-A4E4-FD9A829F389A}"/>
   </bookViews>
@@ -68,9 +68,6 @@
     <t>TC-CHK-003</t>
   </si>
   <si>
-    <t>TC-CHK-004</t>
-  </si>
-  <si>
     <t>TC-CHK-005</t>
   </si>
   <si>
@@ -126,6 +123,9 @@
   </si>
   <si>
     <t>0387877525</t>
+  </si>
+  <si>
+    <t>TC-CHK-007</t>
   </si>
 </sst>
 </file>
@@ -537,7 +537,7 @@
         <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E1" t="s">
         <v>3</v>
@@ -557,126 +557,126 @@
         <v>7</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" t="s">
         <v>12</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E2" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D2" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="E2" s="1" t="s">
+      <c r="F2" t="s">
         <v>14</v>
       </c>
-      <c r="F2" t="s">
-        <v>15</v>
-      </c>
       <c r="G2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" t="s">
         <v>12</v>
       </c>
-      <c r="C3" t="s">
-        <v>13</v>
-      </c>
       <c r="D3" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" t="s">
         <v>12</v>
       </c>
-      <c r="C4" t="s">
+      <c r="D4" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E4" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D4" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>14</v>
-      </c>
       <c r="G4" t="s">
+        <v>19</v>
+      </c>
+      <c r="H4" t="s">
         <v>20</v>
-      </c>
-      <c r="H4" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="B5" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" t="s">
         <v>12</v>
       </c>
-      <c r="C5" t="s">
+      <c r="D5" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E5" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D5" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>14</v>
-      </c>
       <c r="F5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="C6" t="s">
         <v>12</v>
       </c>
-      <c r="C6" t="s">
+      <c r="D6" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="E6" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D6" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>14</v>
-      </c>
       <c r="F6" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G6" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H6" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
   </sheetData>
